--- a/data/trans_dic/IP16B_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores vacunados de la triple vírica</t>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,36; 99,59</t>
+          <t>95,06; 99,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,11; 99,54</t>
+          <t>95,79; 99,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,59; 99,22</t>
+          <t>96,84; 99,32</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,73; 98,66</t>
+          <t>90,91; 98,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,3; 99,08</t>
+          <t>94,81; 99,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,3; 98,4</t>
+          <t>94,16; 98,41</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,52; 100,0</t>
+          <t>91,82; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,71; 100,0</t>
+          <t>96,75; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,23; 99,65</t>
+          <t>95,94; 99,65</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,99; 100,0</t>
+          <t>97,86; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,38; 99,06</t>
+          <t>95,57; 99,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,07; 99,34</t>
+          <t>96,98; 99,29</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>96,4; 99,7</t>
+          <t>96,61; 99,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,45; 99,76</t>
+          <t>97,55; 99,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,85; 99,54</t>
+          <t>97,72; 99,47</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97,14; 100,0</t>
+          <t>96,27; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,58; 99,32</t>
+          <t>90,97; 99,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,75; 99,38</t>
+          <t>94,72; 99,39</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>97,38; 99,06</t>
+          <t>97,54; 99,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>97,13; 98,83</t>
+          <t>97,25; 98,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97,65; 98,77</t>
+          <t>97,73; 98,82</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores vacunados de la triple vírica (tasa de respuesta: 98,91%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>101010</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>133205</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>234214</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>97849; 102517</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>129608; 134724</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>230714; 236610</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>89823</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93292</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>183115</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>85064; 92257</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>90616; 94730</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178097; 186145</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>50731</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63457</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>114188</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>47620; 51861</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61777; 63853</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>111013; 115315</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>214762</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>212707</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>427469</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>211534; 216169</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207892; 215531</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>420591; 430650</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>116369</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>154269</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>270639</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>113789; 117430</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>151979; 155415</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>267334; 272129</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>67333</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67886</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>135220</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>65189; 67712</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>63810; 69660</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>130582; 137018</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>640029</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>724816</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1364845</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>634062; 644497</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>717884; 729525</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1356688; 1371931</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,06; 99,6</t>
+          <t>95,35; 99,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,79; 99,57</t>
+          <t>96,19; 99,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,84; 99,32</t>
+          <t>96,53; 99,27</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,91; 98,59</t>
+          <t>90,81; 98,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,81; 99,12</t>
+          <t>94,45; 99,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,16; 98,41</t>
+          <t>94,15; 98,51</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91,82; 100,0</t>
+          <t>92,0; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,75; 100,0</t>
+          <t>96,44; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95,94; 99,65</t>
+          <t>96,26; 99,66</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,86; 100,0</t>
+          <t>97,71; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,57; 99,08</t>
+          <t>95,53; 99,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,98; 99,29</t>
+          <t>97,26; 99,3</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>96,61; 99,7</t>
+          <t>96,59; 99,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,55; 99,75</t>
+          <t>97,5; 99,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,72; 99,47</t>
+          <t>97,83; 99,58</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96,27; 100,0</t>
+          <t>97,64; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,97; 99,31</t>
+          <t>91,42; 99,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,72; 99,39</t>
+          <t>94,72; 99,41</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,15</t>
+          <t>97,54; 99,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>97,25; 98,82</t>
+          <t>97,3; 98,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97,73; 98,82</t>
+          <t>97,65; 98,79</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97849; 102517</t>
+          <t>98144; 102509</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129608; 134724</t>
+          <t>130146; 134693</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>230714; 236610</t>
+          <t>229974; 236498</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85064; 92257</t>
+          <t>84977; 92250</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90616; 94730</t>
+          <t>90270; 94780</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>178097; 186145</t>
+          <t>178087; 186336</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47620; 51861</t>
+          <t>47714; 51861</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61777; 63853</t>
+          <t>61578; 63853</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111013; 115315</t>
+          <t>111384; 115320</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>211534; 216169</t>
+          <t>211220; 216169</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>207892; 215531</t>
+          <t>207817; 215526</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>420591; 430650</t>
+          <t>421813; 430671</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>113789; 117430</t>
+          <t>113763; 117438</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151979; 155415</t>
+          <t>151899; 155423</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267334; 272129</t>
+          <t>267661; 272437</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>65189; 67712</t>
+          <t>66115; 67712</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63810; 69660</t>
+          <t>64127; 69660</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130582; 137018</t>
+          <t>130584; 137050</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>634062; 644497</t>
+          <t>634059; 644021</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>717884; 729525</t>
+          <t>718305; 729503</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1356688; 1371931</t>
+          <t>1355624; 1371396</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16B_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,35; 99,59</t>
+          <t>96,32; 99,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96,19; 99,55</t>
+          <t>95,2; 99,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,53; 99,27</t>
+          <t>96,69; 99,29</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,81; 98,59</t>
+          <t>95,27; 99,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,45; 99,17</t>
+          <t>91,8; 98,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,15; 98,51</t>
+          <t>94,61; 98,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,0; 100,0</t>
+          <t>97,24; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,44; 100,0</t>
+          <t>93,11; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,26; 99,66</t>
+          <t>95,97; 99,72</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,71; 100,0</t>
+          <t>95,4; 99,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,53; 99,07</t>
+          <t>97,51; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,26; 99,3</t>
+          <t>97,17; 99,34</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>96,59; 99,71</t>
+          <t>97,93; 99,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,5; 99,76</t>
+          <t>96,81; 99,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,83; 99,58</t>
+          <t>98,15; 99,61</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97,64; 100,0</t>
+          <t>90,58; 99,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,42; 99,31</t>
+          <t>97,53; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,72; 99,41</t>
+          <t>94,86; 99,44</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>97,54; 99,08</t>
+          <t>97,23; 98,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>97,3; 98,82</t>
+          <t>97,45; 99,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97,65; 98,79</t>
+          <t>97,78; 98,85</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>151</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>101010</t>
+          <t>119232</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>133205</t>
+          <t>99455</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234214</t>
+          <t>218687</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98144; 102509</t>
+          <t>116511; 120451</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>130146; 134693</t>
+          <t>96439; 100615</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>229974; 236498</t>
+          <t>214916; 220697</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>89823</t>
+          <t>89550</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93292</t>
+          <t>91620</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183115</t>
+          <t>181168</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84977; 92250</t>
+          <t>87071; 90672</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90270; 94780</t>
+          <t>87520; 94206</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>178087; 186336</t>
+          <t>176665; 184027</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>56643</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63457</t>
+          <t>52453</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114188</t>
+          <t>109095</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47714; 51861</t>
+          <t>55372; 56941</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61578; 63853</t>
+          <t>49795; 53482</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111384; 115320</t>
+          <t>105969; 110114</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>272</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>214762</t>
+          <t>196772</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>212707</t>
+          <t>176234</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>427469</t>
+          <t>373006</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>211220; 216169</t>
+          <t>191830; 199205</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>207817; 215526</t>
+          <t>172759; 177167</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>421813; 430671</t>
+          <t>367532; 375748</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>175</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>116369</t>
+          <t>141398</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>154269</t>
+          <t>116165</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270639</t>
+          <t>257563</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>113763; 117438</t>
+          <t>139638; 142291</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151899; 155423</t>
+          <t>113586; 117069</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267661; 272437</t>
+          <t>255098; 258894</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>96</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>64247</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>67886</t>
+          <t>68856</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>135220</t>
+          <t>133101</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66115; 67712</t>
+          <t>60224; 66062</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64127; 69660</t>
+          <t>67487; 69194</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130584; 137050</t>
+          <t>128709; 134914</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>902</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>640029</t>
+          <t>667840</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>724816</t>
+          <t>604782</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1364845</t>
+          <t>1272620</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>634059; 644021</t>
+          <t>660657; 671981</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>718305; 729503</t>
+          <t>598143; 608278</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1355624; 1371396</t>
+          <t>1264500; 1278371</t>
         </is>
       </c>
     </row>
